--- a/__DATACENTER/T6_VALIDATE/MACCRE_Swarm_Request.xlsx
+++ b/__DATACENTER/T6_VALIDATE/MACCRE_Swarm_Request.xlsx
@@ -1368,7 +1368,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Orphan node — unreachable. Routes to a nonexistent target.</t>
+          <t>Orphan node — unreachable. Routes to a nonexistent target. Also waits for a ghost node.</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr"/>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>GHOST_NODE</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
